--- a/RSI Modular - copia/tabla_maestra_EPU.xlsx
+++ b/RSI Modular - copia/tabla_maestra_EPU.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,22 +507,22 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>0.83</v>
       </c>
       <c r="G2" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="H2" t="n">
         <v>1.26</v>
       </c>
       <c r="I2" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.41</v>
+        <v>4.24</v>
       </c>
       <c r="K2" t="n">
         <v>8.65</v>
@@ -589,25 +589,25 @@
         <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>2.89</v>
       </c>
       <c r="J4" t="n">
-        <v>7.18</v>
+        <v>7.02</v>
       </c>
       <c r="K4" t="n">
-        <v>11.39</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="5">
@@ -639,7 +639,7 @@
         <v>-1.1</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.82</v>
+        <v>-1.81</v>
       </c>
       <c r="I5" t="n">
         <v>-4.72</v>
@@ -804,28 +804,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.19</v>
+        <v>-0.64</v>
       </c>
       <c r="G10" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>2.99</v>
       </c>
       <c r="J10" t="n">
-        <v>4.8</v>
+        <v>5.29</v>
       </c>
       <c r="K10" t="n">
-        <v>9.42</v>
+        <v>9.25</v>
       </c>
     </row>
     <row r="11">
@@ -943,25 +943,25 @@
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.53</v>
+        <v>-0.43</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8</v>
+        <v>0.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1.01</v>
+        <v>0.38</v>
       </c>
       <c r="H14" t="n">
-        <v>1.93</v>
+        <v>1.14</v>
       </c>
       <c r="I14" t="n">
-        <v>5.04</v>
+        <v>4.12</v>
       </c>
       <c r="J14" t="n">
-        <v>4.37</v>
+        <v>3.26</v>
       </c>
       <c r="K14" t="n">
-        <v>8.83</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="15">
@@ -1113,31 +1113,58 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RSI(45)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30/70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>7</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>0.7</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>0.19</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>-0.08</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>-0.29</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>-0.23</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>-6.51</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>-22.64</v>
       </c>
     </row>
@@ -1152,7 +1179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,10 +1259,10 @@
         <v>14</v>
       </c>
       <c r="E2" t="n">
-        <v>42.9</v>
+        <v>35.7</v>
       </c>
       <c r="F2" t="n">
-        <v>64.3</v>
+        <v>57.1</v>
       </c>
       <c r="G2" t="n">
         <v>64.3</v>
@@ -1364,7 +1391,7 @@
         <v>43.1</v>
       </c>
       <c r="H5" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="I5" t="n">
         <v>26.8</v>
@@ -1529,28 +1556,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>38.5</v>
+        <v>41.7</v>
       </c>
       <c r="F10" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>46.2</v>
+        <v>41.7</v>
       </c>
       <c r="H10" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
-        <v>53.8</v>
+        <v>58.3</v>
       </c>
       <c r="J10" t="n">
-        <v>53.8</v>
+        <v>58.3</v>
       </c>
       <c r="K10" t="n">
-        <v>84.59999999999999</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="11">
@@ -1668,7 +1695,7 @@
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="F14" t="n">
         <v>83.3</v>
@@ -1838,31 +1865,58 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RSI(45)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30/70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>7</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E20" t="n">
         <v>71.40000000000001</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>42.9</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G20" t="n">
         <v>42.9</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H20" t="n">
         <v>57.1</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>42.9</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J20" t="n">
         <v>28.6</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1877,7 +1931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1958,11 +2012,7 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>*</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
@@ -2258,13 +2308,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -2561,11 +2615,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -2573,7 +2627,34 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RSI(45)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>30/70</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>**</t>
         </is>
